--- a/test/moe_w8a8/moegemmoutput.xlsx
+++ b/test/moe_w8a8/moegemmoutput.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>32768</v>
       </c>
       <c r="B2" t="n">
         <v>256</v>
@@ -477,12 +477,12 @@
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>168.4550259113312</v>
+        <v>31357.85543823242</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>49152</v>
       </c>
       <c r="B3" t="n">
         <v>256</v>
@@ -497,12 +497,12 @@
         <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>197.8898788690567</v>
+        <v>34425.97329711914</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>65536</v>
       </c>
       <c r="B4" t="n">
         <v>256</v>
@@ -517,12 +517,12 @@
         <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>244.3989465236664</v>
+        <v>61505.47698974609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>131072</v>
       </c>
       <c r="B5" t="n">
         <v>256</v>
@@ -537,247 +537,7 @@
         <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>346.2601265907288</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B6" t="n">
-        <v>256</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E6" t="n">
-        <v>128</v>
-      </c>
-      <c r="F6" t="n">
-        <v>500.7967615127563</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B7" t="n">
-        <v>256</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E7" t="n">
-        <v>128</v>
-      </c>
-      <c r="F7" t="n">
-        <v>667.2647843360901</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>64</v>
-      </c>
-      <c r="B8" t="n">
-        <v>256</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E8" t="n">
-        <v>128</v>
-      </c>
-      <c r="F8" t="n">
-        <v>869.4522542953491</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128</v>
-      </c>
-      <c r="B9" t="n">
-        <v>256</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F9" t="n">
-        <v>991.1409406661987</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>256</v>
-      </c>
-      <c r="B10" t="n">
-        <v>256</v>
-      </c>
-      <c r="C10" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D10" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E10" t="n">
-        <v>128</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1075.584070205688</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>512</v>
-      </c>
-      <c r="B11" t="n">
-        <v>256</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E11" t="n">
-        <v>128</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1278.132204055786</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1024</v>
-      </c>
-      <c r="B12" t="n">
-        <v>256</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E12" t="n">
-        <v>128</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1687.069597244263</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B13" t="n">
-        <v>256</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E13" t="n">
-        <v>128</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2518.172309875488</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4096</v>
-      </c>
-      <c r="B14" t="n">
-        <v>256</v>
-      </c>
-      <c r="C14" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E14" t="n">
-        <v>128</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4088.561676025391</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>6144</v>
-      </c>
-      <c r="B15" t="n">
-        <v>256</v>
-      </c>
-      <c r="C15" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E15" t="n">
-        <v>128</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5764.517024993896</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8192</v>
-      </c>
-      <c r="B16" t="n">
-        <v>256</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E16" t="n">
-        <v>128</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7647.940353393555</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16384</v>
-      </c>
-      <c r="B17" t="n">
-        <v>256</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7168</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7168</v>
-      </c>
-      <c r="E17" t="n">
-        <v>128</v>
-      </c>
-      <c r="F17" t="n">
-        <v>15412.26986694336</v>
+        <v>124707.2777099609</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/moegemmoutput.xlsx
+++ b/test/moe_w8a8/moegemmoutput.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32768</v>
+        <v>1024</v>
       </c>
       <c r="B2" t="n">
         <v>256</v>
@@ -477,12 +477,12 @@
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>31357.85543823242</v>
+        <v>1395.919703483582</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49152</v>
+        <v>2048</v>
       </c>
       <c r="B3" t="n">
         <v>256</v>
@@ -497,12 +497,12 @@
         <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>34425.97329711914</v>
+        <v>1883.382879257202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65536</v>
+        <v>4096</v>
       </c>
       <c r="B4" t="n">
         <v>256</v>
@@ -517,12 +517,12 @@
         <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>61505.47698974609</v>
+        <v>2946.347919464111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131072</v>
+        <v>6144</v>
       </c>
       <c r="B5" t="n">
         <v>256</v>
@@ -537,7 +537,47 @@
         <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>124707.2777099609</v>
+        <v>4358.485771179199</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8192</v>
+      </c>
+      <c r="B6" t="n">
+        <v>256</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7168</v>
+      </c>
+      <c r="E6" t="n">
+        <v>128</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5580.078716278076</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16384</v>
+      </c>
+      <c r="B7" t="n">
+        <v>256</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7168</v>
+      </c>
+      <c r="E7" t="n">
+        <v>128</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9671.560157775879</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/moegemmoutput.xlsx
+++ b/test/moe_w8a8/moegemmoutput.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1024</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>256</v>
@@ -477,12 +477,12 @@
         <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>1395.919703483582</v>
+        <v>158.2975109815598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2048</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>256</v>
@@ -497,12 +497,12 @@
         <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>1883.382879257202</v>
+        <v>180.5454915761948</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4096</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
         <v>256</v>
@@ -517,12 +517,12 @@
         <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>2946.347919464111</v>
+        <v>225.8557105064392</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6144</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>256</v>
@@ -537,12 +537,12 @@
         <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>4358.485771179199</v>
+        <v>301.1489403247833</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8192</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
         <v>256</v>
@@ -557,12 +557,12 @@
         <v>128</v>
       </c>
       <c r="F6" t="n">
-        <v>5580.078716278076</v>
+        <v>419.2741546630859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16384</v>
+        <v>32</v>
       </c>
       <c r="B7" t="n">
         <v>256</v>
@@ -577,7 +577,47 @@
         <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>9671.560157775879</v>
+        <v>579.0929403305054</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B8" t="n">
+        <v>256</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7168</v>
+      </c>
+      <c r="E8" t="n">
+        <v>128</v>
+      </c>
+      <c r="F8" t="n">
+        <v>725.3000640869141</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128</v>
+      </c>
+      <c r="B9" t="n">
+        <v>256</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7168</v>
+      </c>
+      <c r="E9" t="n">
+        <v>128</v>
+      </c>
+      <c r="F9" t="n">
+        <v>828.1709146499634</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/moegemmoutput.xlsx
+++ b/test/moe_w8a8/moegemmoutput.xlsx
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C2" t="n">
         <v>7168</v>
@@ -474,10 +474,10 @@
         <v>7168</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F2" t="n">
-        <v>158.2975109815598</v>
+        <v>141.8223965167999</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C3" t="n">
         <v>7168</v>
@@ -494,10 +494,10 @@
         <v>7168</v>
       </c>
       <c r="E3" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F3" t="n">
-        <v>180.5454915761948</v>
+        <v>186.0018619298935</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C4" t="n">
         <v>7168</v>
@@ -514,10 +514,10 @@
         <v>7168</v>
       </c>
       <c r="E4" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F4" t="n">
-        <v>225.8557105064392</v>
+        <v>261.4665768146515</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C5" t="n">
         <v>7168</v>
@@ -534,10 +534,10 @@
         <v>7168</v>
       </c>
       <c r="E5" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F5" t="n">
-        <v>301.1489403247833</v>
+        <v>400.9427406787872</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C6" t="n">
         <v>7168</v>
@@ -554,10 +554,10 @@
         <v>7168</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F6" t="n">
-        <v>419.2741546630859</v>
+        <v>617.7588090896606</v>
       </c>
     </row>
     <row r="7">
@@ -565,7 +565,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C7" t="n">
         <v>7168</v>
@@ -574,10 +574,10 @@
         <v>7168</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F7" t="n">
-        <v>579.0929403305054</v>
+        <v>927.7157583236694</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>64</v>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C8" t="n">
         <v>7168</v>
@@ -594,10 +594,10 @@
         <v>7168</v>
       </c>
       <c r="E8" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>725.3000640869141</v>
+        <v>1208.196397781372</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
         <v>128</v>
       </c>
       <c r="B9" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="C9" t="n">
         <v>7168</v>
@@ -614,10 +614,10 @@
         <v>7168</v>
       </c>
       <c r="E9" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="F9" t="n">
-        <v>828.1709146499634</v>
+        <v>1392.223101615906</v>
       </c>
     </row>
   </sheetData>

--- a/test/moe_w8a8/moegemmoutput.xlsx
+++ b/test/moe_w8a8/moegemmoutput.xlsx
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C2" t="n">
         <v>7168</v>
@@ -474,10 +474,10 @@
         <v>7168</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F2" t="n">
-        <v>141.8223965167999</v>
+        <v>129.0806521177292</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C3" t="n">
         <v>7168</v>
@@ -494,10 +494,10 @@
         <v>7168</v>
       </c>
       <c r="E3" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>186.0018619298935</v>
+        <v>153.1943862438202</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C4" t="n">
         <v>7168</v>
@@ -514,10 +514,10 @@
         <v>7168</v>
       </c>
       <c r="E4" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>261.4665768146515</v>
+        <v>189.4929033517838</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
         <v>7168</v>
@@ -534,10 +534,10 @@
         <v>7168</v>
       </c>
       <c r="E5" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>400.9427406787872</v>
+        <v>260.8761825561523</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
         <v>7168</v>
@@ -554,10 +554,10 @@
         <v>7168</v>
       </c>
       <c r="E6" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F6" t="n">
-        <v>617.7588090896606</v>
+        <v>372.6007015705109</v>
       </c>
     </row>
     <row r="7">
@@ -565,7 +565,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
         <v>7168</v>
@@ -574,10 +574,10 @@
         <v>7168</v>
       </c>
       <c r="E7" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>927.7157583236694</v>
+        <v>519.4661426544189</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         <v>64</v>
       </c>
       <c r="B8" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C8" t="n">
         <v>7168</v>
@@ -594,10 +594,10 @@
         <v>7168</v>
       </c>
       <c r="E8" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F8" t="n">
-        <v>1208.196397781372</v>
+        <v>676.2187595367432</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
         <v>128</v>
       </c>
       <c r="B9" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C9" t="n">
         <v>7168</v>
@@ -614,10 +614,10 @@
         <v>7168</v>
       </c>
       <c r="E9" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
-        <v>1392.223101615906</v>
+        <v>769.4474658966064</v>
       </c>
     </row>
   </sheetData>
